--- a/data/trans_dic/P57_AF_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57_AF_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke)</t>
+          <t>Población con apoyo afectivo bajo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,21; 70,11</t>
+          <t>64,25; 70,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,41; 69,86</t>
+          <t>63,11; 69,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,17; 78,56</t>
+          <t>72,34; 78,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,49; 66,83</t>
+          <t>58,52; 66,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,64; 69,82</t>
+          <t>64,94; 69,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,04; 72,03</t>
+          <t>67,09; 72,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,25; 83,45</t>
+          <t>78,36; 83,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,25; 68,43</t>
+          <t>63,16; 68,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65,47; 69,22</t>
+          <t>65,28; 69,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66,56; 70,26</t>
+          <t>66,45; 70,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76,51; 80,37</t>
+          <t>76,62; 80,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,28; 66,82</t>
+          <t>62,45; 66,92</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,6; 60,38</t>
+          <t>55,48; 60,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,19; 62,82</t>
+          <t>58,05; 62,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,06; 77,12</t>
+          <t>73,13; 77,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,41; 56,33</t>
+          <t>30,99; 56,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,32; 61,43</t>
+          <t>56,6; 61,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,96; 69,66</t>
+          <t>64,83; 69,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,72; 78,57</t>
+          <t>74,69; 78,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>53,16; 70,95</t>
+          <t>52,17; 69,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56,85; 60,34</t>
+          <t>56,81; 60,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61,75; 65,04</t>
+          <t>61,87; 65,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74,7; 77,38</t>
+          <t>74,62; 77,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,9; 59,98</t>
+          <t>46,14; 59,75</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,12; 61,03</t>
+          <t>51,76; 61,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,92; 63,93</t>
+          <t>53,23; 62,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,69; 71,04</t>
+          <t>62,81; 70,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,43; 55,76</t>
+          <t>46,83; 55,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,9; 56,37</t>
+          <t>46,71; 55,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,7; 61,73</t>
+          <t>52,35; 61,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,71; 69,17</t>
+          <t>60,72; 68,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,87; 50,51</t>
+          <t>44,11; 50,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,07; 57,54</t>
+          <t>50,96; 57,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,93; 61,12</t>
+          <t>53,85; 61,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63,12; 68,95</t>
+          <t>63,14; 68,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,69; 52,0</t>
+          <t>46,47; 52,1</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,15; 62,57</t>
+          <t>59,03; 62,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,24; 63,68</t>
+          <t>60,29; 63,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,45; 75,45</t>
+          <t>72,44; 75,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,47; 56,5</t>
+          <t>40,37; 56,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,51; 62,8</t>
+          <t>59,65; 62,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,0; 68,38</t>
+          <t>65,04; 68,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,32; 77,53</t>
+          <t>74,66; 77,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,51; 65,99</t>
+          <t>54,63; 65,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,81; 62,09</t>
+          <t>59,72; 62,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63,21; 65,54</t>
+          <t>63,21; 65,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,88; 76,0</t>
+          <t>74,04; 76,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,92; 59,03</t>
+          <t>49,33; 58,99</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo afectivo bajo (Duke)</t>
+          <t>Población con apoyo afectivo bajo (Duke) (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>662495; 723307</t>
+          <t>662902; 723954</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>611230; 673476</t>
+          <t>608395; 668937</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>540990; 588866</t>
+          <t>542267; 588644</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>297976; 340487</t>
+          <t>298133; 338647</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>850128; 918215</t>
+          <t>854095; 917861</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>887310; 953344</t>
+          <t>887999; 955165</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>776588; 828223</t>
+          <t>777714; 829668</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>467260; 505493</t>
+          <t>466538; 506789</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1536429; 1624402</t>
+          <t>1531975; 1625533</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1522600; 1607309</t>
+          <t>1520089; 1608451</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1332888; 1400060</t>
+          <t>1334853; 1405095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>777337; 834069</t>
+          <t>779556; 835296</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>940668; 1021540</t>
+          <t>938488; 1020549</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1138734; 1229333</t>
+          <t>1135999; 1229870</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1510615; 1594641</t>
+          <t>1512117; 1592951</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>737623; 1281998</t>
+          <t>705308; 1278066</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>893044; 974017</t>
+          <t>897539; 972381</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1136200; 1218376</t>
+          <t>1133862; 1214336</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1477532; 1553575</t>
+          <t>1477003; 1556200</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1183481; 1579523</t>
+          <t>1161481; 1551024</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1863380; 1977621</t>
+          <t>1862047; 1979611</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2288480; 2410198</t>
+          <t>2292825; 2417995</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3021563; 3130094</t>
+          <t>3018491; 3131319</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2066363; 2700353</t>
+          <t>2077442; 2689969</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>285940; 334807</t>
+          <t>283932; 335759</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>257699; 305535</t>
+          <t>254393; 300350</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>341717; 387229</t>
+          <t>342373; 386739</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>303711; 357027</t>
+          <t>299881; 354019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>223442; 268551</t>
+          <t>222525; 265933</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>235393; 281062</t>
+          <t>238330; 281916</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>329974; 375982</t>
+          <t>330029; 373619</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>288606; 332301</t>
+          <t>290152; 332464</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>523473; 589796</t>
+          <t>522364; 589821</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>503218; 570398</t>
+          <t>502475; 569673</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>687149; 750587</t>
+          <t>687289; 748778</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>606113; 674967</t>
+          <t>603202; 676267</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1935520; 2047449</t>
+          <t>1931499; 2040308</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2047477; 2164208</t>
+          <t>2048982; 2159191</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2435905; 2536806</t>
+          <t>2435717; 2536367</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1352082; 1935428</t>
+          <t>1383064; 1939865</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2009712; 2120774</t>
+          <t>2014386; 2124563</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2293157; 2412532</t>
+          <t>2294574; 2416977</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2611302; 2724069</t>
+          <t>2623007; 2724409</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1974915; 2390508</t>
+          <t>1979105; 2386471</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3977174; 4128712</t>
+          <t>3970701; 4129880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4378457; 4539692</t>
+          <t>4378185; 4545095</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5079675; 5225346</t>
+          <t>5091048; 5235640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3448349; 4160619</t>
+          <t>3476998; 4158198</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_AF_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57_AF_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,25; 70,17</t>
+          <t>63,98; 69,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,11; 69,39</t>
+          <t>63,21; 69,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,34; 78,53</t>
+          <t>72,45; 78,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,52; 66,47</t>
+          <t>59,61; 67,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,94; 69,79</t>
+          <t>64,67; 69,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,09; 72,17</t>
+          <t>67,01; 72,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,36; 83,59</t>
+          <t>78,08; 83,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,16; 68,6</t>
+          <t>64,15; 69,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65,28; 69,26</t>
+          <t>65,52; 69,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66,45; 70,31</t>
+          <t>66,33; 70,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76,62; 80,65</t>
+          <t>76,42; 80,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,45; 66,92</t>
+          <t>63,05; 67,38</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,48; 60,33</t>
+          <t>55,61; 60,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,05; 62,85</t>
+          <t>58,08; 62,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,13; 77,04</t>
+          <t>73,27; 77,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,99; 56,15</t>
+          <t>54,72; 59,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,6; 61,32</t>
+          <t>56,5; 61,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,83; 69,43</t>
+          <t>65,06; 69,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,69; 78,7</t>
+          <t>74,91; 78,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,17; 69,67</t>
+          <t>56,45; 60,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56,81; 60,4</t>
+          <t>56,89; 60,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61,87; 65,25</t>
+          <t>61,93; 65,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74,62; 77,41</t>
+          <t>74,61; 77,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,14; 59,75</t>
+          <t>56,21; 59,36</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,51%</t>
         </is>
       </c>
     </row>
@@ -997,42 +997,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51,76; 61,21</t>
+          <t>52,26; 60,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,23; 62,85</t>
+          <t>53,19; 63,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,81; 70,95</t>
+          <t>62,59; 71,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,83; 55,29</t>
+          <t>47,1; 55,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,71; 55,82</t>
+          <t>46,7; 56,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,35; 61,92</t>
+          <t>51,73; 61,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,72; 68,74</t>
+          <t>60,76; 68,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,11; 50,54</t>
+          <t>44,69; 51,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,85; 61,05</t>
+          <t>54,13; 61,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63,14; 68,78</t>
+          <t>63,03; 68,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,47; 52,1</t>
+          <t>47,02; 52,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,03; 62,36</t>
+          <t>58,95; 62,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,29; 63,53</t>
+          <t>60,02; 63,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,44; 75,44</t>
+          <t>72,41; 75,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40,37; 56,63</t>
+          <t>54,96; 58,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,65; 62,91</t>
+          <t>59,65; 62,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,04; 68,51</t>
+          <t>65,14; 68,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,66; 77,54</t>
+          <t>74,71; 77,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,63; 65,87</t>
+          <t>56,7; 59,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,72; 62,11</t>
+          <t>59,76; 62,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63,21; 65,62</t>
+          <t>63,04; 65,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74,04; 76,15</t>
+          <t>73,95; 76,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,33; 58,99</t>
+          <t>56,53; 58,86</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>320059</t>
+          <t>362650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>487015</t>
+          <t>536410</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>807074</t>
+          <t>899060</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>662902; 723954</t>
+          <t>660055; 720434</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>608395; 668937</t>
+          <t>609316; 670083</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>542267; 588644</t>
+          <t>543060; 590584</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>298133; 338647</t>
+          <t>341644; 384065</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>854095; 917861</t>
+          <t>850491; 919985</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>887999; 955165</t>
+          <t>886941; 955543</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>777714; 829668</t>
+          <t>774927; 831756</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>466538; 506789</t>
+          <t>515309; 555406</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1531975; 1625533</t>
+          <t>1537540; 1627173</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1520089; 1608451</t>
+          <t>1517396; 1610271</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1334853; 1405095</t>
+          <t>1331276; 1400625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>779556; 835296</t>
+          <t>867871; 927412</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1127919</t>
+          <t>1265117</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1313565</t>
+          <t>1261551</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2441483</t>
+          <t>2526668</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>938488; 1020549</t>
+          <t>940701; 1022048</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1135999; 1229870</t>
+          <t>1136639; 1221318</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1512117; 1592951</t>
+          <t>1515032; 1592757</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>705308; 1278066</t>
+          <t>1211775; 1322041</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>897539; 972381</t>
+          <t>895977; 975341</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1133862; 1214336</t>
+          <t>1137958; 1217253</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1477003; 1556200</t>
+          <t>1481295; 1553637</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1161481; 1551024</t>
+          <t>1218939; 1307115</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1862047; 1979611</t>
+          <t>1864641; 1973384</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2292825; 2417995</t>
+          <t>2295147; 2417744</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3018491; 3131319</t>
+          <t>3018184; 3133116</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2077442; 2689969</t>
+          <t>2458265; 2596278</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328054</t>
+          <t>360570</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>310868</t>
+          <t>350403</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>638922</t>
+          <t>710973</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>283932; 335759</t>
+          <t>286674; 334252</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>254393; 300350</t>
+          <t>254205; 301579</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>342373; 386739</t>
+          <t>341136; 387396</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>299881; 354019</t>
+          <t>332124; 390328</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>222525; 265933</t>
+          <t>222473; 267526</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>238330; 281916</t>
+          <t>235528; 279691</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>330029; 373619</t>
+          <t>330235; 373884</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>290152; 332464</t>
+          <t>326608; 374605</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>522364; 589821</t>
+          <t>522330; 589788</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>502475; 569673</t>
+          <t>505146; 570044</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>687289; 748778</t>
+          <t>686115; 746639</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>603202; 676267</t>
+          <t>675181; 750085</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1776030</t>
+          <t>1988338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2111448</t>
+          <t>2148364</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3887479</t>
+          <t>4136702</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1931499; 2040308</t>
+          <t>1929022; 2039205</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2048982; 2159191</t>
+          <t>2039954; 2157658</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2435717; 2536367</t>
+          <t>2434535; 2537318</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1383064; 1939865</t>
+          <t>1919659; 2054195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2014386; 2124563</t>
+          <t>2014582; 2123827</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2294574; 2416977</t>
+          <t>2297922; 2414048</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2623007; 2724409</t>
+          <t>2624840; 2721643</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1979105; 2386471</t>
+          <t>2094247; 2204668</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3970701; 4129880</t>
+          <t>3973465; 4136987</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4378185; 4545095</t>
+          <t>4366911; 4541182</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5091048; 5235640</t>
+          <t>5084530; 5236640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3476998; 4158198</t>
+          <t>4062126; 4229896</t>
         </is>
       </c>
     </row>
